--- a/astro-site/public/dl/kit-escandallos/08-food-truck.xlsx
+++ b/astro-site/public/dl/kit-escandallos/08-food-truck.xlsx
@@ -23,7 +23,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Pulled Pork Sándwich'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Pulled Pork Sándwich'!$A$1:$J$35</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Punto de Equilibrio'!$A$1:$J$28</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Conversiones'!$A$1:$J$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Conversiones'!$A$1:$J$67</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'Mermas'!$A$1:$J$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1037,7 +1037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B65"/>
+  <dimension ref="A1:B66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1152,256 +1152,263 @@
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>▸ Cantidad: la que usas en el plato, EN LA UNIDAD DE USO.</t>
+          <t>▸ ¿Llevas tus precios en la plantilla 13 (Lista de Precios de Ingredientes)? Lleva su «Precio por unidad base» a «Precio/Ud (€)» con Pegado especial → Valores (en Excel, Ctrl+Alt+V y luego V) y pon esa misma unidad en «Ud. Compra». Un pegado normal arrastraría la fórmula: el precio y el coste de esa línea se quedarían en blanco sin avisar, y el coste del plato saldría más bajo.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>▸ Ud. Uso: la unidad en la que mides al cocinar (g, ml, cl, ud…).</t>
+          <t>▸ Cantidad: la que usas en el plato, EN LA UNIDAD DE USO.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>▸ Factor: conversión automática Ud. Compra → Ud. Uso, de la hoja «Conversiones». Si la pareja NO está en la tabla, el Factor se pone en rojo con un «?» y el Coste dice «revisa unidades»: añade la equivalencia en «Conversiones» antes de fiarte del número. Nunca da un coste plausible y falso.</t>
+          <t>▸ Ud. Uso: la unidad en la que mides al cocinar (g, ml, cl, ud…).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>▸ Merma (%): desperdicio. En las filas de ejemplo está escrita a mano; en las vacías la trae la hoja «Mermas» en cuanto eliges categoría, y puedes escribir encima.</t>
+          <t>▸ Factor: conversión automática Ud. Compra → Ud. Uso, de la hoja «Conversiones». Si la pareja NO está en la tabla, el Factor se pone en rojo con un «?» y el Coste dice «revisa unidades»: añade la equivalencia en «Conversiones» antes de fiarte del número. Nunca da un coste plausible y falso.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>▸ Ojo con la merma cuando mides en PIEZAS: la del 11 % de los huevos es la CÁSCARA, y sólo tiene sentido sobre el peso. Si compras y mides en unidades, déjala en 0 %: seis huevos son seis huevos, no 6,74. La misma regla vale para cualquier ingrediente que cuentes por unidad.</t>
+          <t>▸ Merma (%): desperdicio. En las filas de ejemplo está escrita a mano; en las vacías la trae la hoja «Mermas» en cuanto eliges categoría, y puedes escribir encima.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>▸ Cant. Bruta: lo que hay que comprar contando la merma (automático).</t>
+          <t>▸ Ojo con la merma cuando mides en PIEZAS: la del 11 % de los huevos es la CÁSCARA, y sólo tiene sentido sobre el peso. Si compras y mides en unidades, déjala en 0 %: seis huevos son seis huevos, no 6,74. La misma regla vale para cualquier ingrediente que cuentes por unidad.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="6" t="inlineStr">
         <is>
+          <t>▸ Cant. Bruta: lo que hay que comprar contando la merma (automático).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="6" t="inlineStr">
+        <is>
           <t>▸ Coste (€): Cant. Bruta × Precio/Ud ÷ Factor (automático).</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="B28" s="4" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Bloque de resultado</t>
         </is>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>▸ Coste elaboración (%): recargo sobre la materia prima para cubrir energía, envasado y pérdidas de preparación que no se escandallan línea a línea. Viene al 10 %; ponlo a 0 % si prefieres imputar esos costes aparte.</t>
-        </is>
-      </c>
-    </row>
+    <row r="30"/>
     <row r="31">
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>▸ COSTE TOTAL DEL PLATO: materia prima + coste de elaboración.</t>
+          <t>▸ Coste elaboración (%): recargo sobre la materia prima para cubrir energía, envasado y pérdidas de preparación que no se escandallan línea a línea. Viene al 10 %; ponlo a 0 % si prefieres imputar esos costes aparte.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>▸ Nº de raciones: cuántas raciones salen de lo escandallado. Déjalo en 1 si es un plato individual.</t>
+          <t>▸ COSTE TOTAL DEL PLATO: materia prima + coste de elaboración.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>▸ COSTE POR RACIÓN: coste total ÷ raciones. Es la base del PVP.</t>
+          <t>▸ Nº de raciones: cuántas raciones salen de lo escandallado. Déjalo en 1 si es un plato individual.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>▸ Food Cost objetivo (%): el que quieres conseguir. PVP sin IVA = coste por ración ÷ food cost objetivo.</t>
+          <t>▸ COSTE POR RACIÓN: coste total ÷ raciones. Es la base del PVP.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>▸ Tipo de IVA (%): editable. 10 % en hostelería en España; cámbialo si te aplica otro tipo (IGIC en Canarias, o el IVA/ITBIS/IVU de tu país en Latinoamérica).</t>
+          <t>▸ Food Cost objetivo (%): el que quieres conseguir. PVP sin IVA = coste por ración ÷ food cost objetivo.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>▸ PVP actual en carta (sin IVA): lo que cobras HOY. Déjalo vacío si todavía no lo tienes.</t>
+          <t>▸ Tipo de IVA (%): editable. 10 % en hostelería en España; cámbialo si te aplica otro tipo (IGIC en Canarias, o el IVA/ITBIS/IVU de tu país en Latinoamérica).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="6" t="inlineStr">
         <is>
+          <t>▸ PVP actual en carta (sin IVA): lo que cobras HOY. Déjalo vacío si todavía no lo tienes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="6" t="inlineStr">
+        <is>
           <t>▸ FOOD COST REAL (%): coste por ración ÷ PVP actual. Se pone en rojo en cuanto supera tu objetivo.</t>
         </is>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="B39" s="4" t="inlineStr">
+    <row r="39"/>
+    <row r="40">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>Hojas auxiliares</t>
         </is>
       </c>
     </row>
-    <row r="40"/>
-    <row r="41">
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>▸ «Conversiones»: equivalencias Ud. Compra → Ud. Uso. Va SIN protección: añade las parejas que te falten y corrige el tamaño de los formatos (la botella viene a 70 cl y la lata a 33 cl; si tu vino es de 75 cl, cambia el 70 por 75 en «botella→cl»).</t>
-        </is>
-      </c>
-    </row>
+    <row r="41"/>
     <row r="42">
       <c r="B42" s="6" t="inlineStr">
         <is>
+          <t>▸ «Conversiones»: equivalencias Ud. Compra → Ud. Uso. Va SIN protección: añade las parejas que te falten y corrige el tamaño de los formatos (la botella viene a 70 cl y la lata a 33 cl; si tu vino es de 75 cl, cambia el 70 por 75 en «botella→cl»).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="6" t="inlineStr">
+        <is>
           <t>▸ «Mermas»: merma mínima, típica y máxima por categoría. La típica es la que se precarga en las filas vacías.</t>
         </is>
       </c>
     </row>
-    <row r="43"/>
-    <row r="44">
-      <c r="B44" s="4" t="inlineStr">
+    <row r="44"/>
+    <row r="45">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Protección de la hoja</t>
         </is>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46">
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>▸ Las hojas están protegidas SIN contraseña para que no borres una fórmula sin querer: sólo se escriben las celdas verdes.</t>
-        </is>
-      </c>
-    </row>
+    <row r="46"/>
     <row r="47">
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>▸ Para tocar cualquier otra cosa —insertar filas, pegar la foto del plato, cambiar una fórmula—: Revisar → Desproteger hoja. No pide contraseña.</t>
+          <t>▸ Las hojas están protegidas SIN contraseña para que no borres una fórmula sin querer: sólo se escriben las celdas verdes.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>▸ Si te quedas sin filas: desprotege la hoja e inserta filas DENTRO del bloque de ingredientes (clic derecho sobre una fila del bloque → Insertar), nunca debajo de la última. Así el «COSTE TOTAL INGREDIENTES» las recoge solo; lo que escribas por debajo del bloque NO suma.</t>
+          <t>▸ Para tocar cualquier otra cosa —insertar filas, pegar la foto del plato, cambiar una fórmula—: Revisar → Desproteger hoja. No pide contraseña.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="6" t="inlineStr">
         <is>
+          <t>▸ Si te quedas sin filas: desprotege la hoja e inserta filas DENTRO del bloque de ingredientes (clic derecho sobre una fila del bloque → Insertar), nunca debajo de la última. Así el «COSTE TOTAL INGREDIENTES» las recoge solo; lo que escribas por debajo del bloque NO suma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="6" t="inlineStr">
+        <is>
           <t>▸ La foto del plato NO se puede arrastrar con la hoja protegida: primero Revisar → Desproteger hoja, y después Insertar → Imagen.</t>
         </is>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51">
-      <c r="B51" s="4" t="inlineStr">
+    <row r="51"/>
+    <row r="52">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>Referencia de mermas estándar</t>
         </is>
       </c>
     </row>
-    <row r="52"/>
-    <row r="53">
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>▸ Carne roja 20 % | Aves 25 % | Pescado 35 % | Marisco 45 %</t>
-        </is>
-      </c>
-    </row>
+    <row r="53"/>
     <row r="54">
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>▸ Verdura hoja 25 % | Verdura raíz 12 % | Verdura fruto 10 % | Fruta 15 %</t>
+          <t>▸ Carne roja 20 % | Aves 25 % | Pescado 35 % | Marisco 45 %</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>▸ Lácteos 3 % | Secos/granos 2 % | Congelados 7 % | Pan/bollería 5 %</t>
+          <t>▸ Verdura hoja 25 % | Verdura raíz 12 % | Verdura fruto 10 % | Fruta 15 %</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>▸ Huevos 11 % | Aceites/grasas 3 % | Especias/hierbas 20 % | Chocolate/cacao 5 %</t>
+          <t>▸ Lácteos 3 % | Secos/granos 2 % | Congelados 7 % | Pan/bollería 5 %</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>▸ Bebidas/licores 2 % | Setas/hongos 20 % | Conservas/encurtidos 8 % | Salsas/condimentos 5 %</t>
+          <t>▸ Huevos 11 % | Aceites/grasas 3 % | Especias/hierbas 20 % | Chocolate/cacao 5 %</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>▸ Pasta/arroz 2 %</t>
+          <t>▸ Bebidas/licores 2 % | Setas/hongos 20 % | Conservas/encurtidos 8 % | Salsas/condimentos 5 %</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="6" t="inlineStr">
         <is>
+          <t>▸ Pasta/arroz 2 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="6" t="inlineStr">
+        <is>
           <t>▸ Son las 21 categorías del desplegable. La tabla completa, con mínimo y máximo, está en la hoja «Mermas».</t>
         </is>
       </c>
     </row>
-    <row r="60"/>
-    <row r="61">
-      <c r="B61" s="6" t="inlineStr">
+    <row r="61"/>
+    <row r="62">
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>— Kit de Escandallos Pro · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
-    <row r="62"/>
-    <row r="63">
-      <c r="B63" s="6" t="inlineStr">
+    <row r="63"/>
+    <row r="64">
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · Todos los derechos reservados</t>
         </is>
       </c>
     </row>
-    <row r="64"/>
-    <row r="65">
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-escandallos · info@aichef.pro</t>
+    <row r="65"/>
+    <row r="66">
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>Versión 2.1 · septiembre 2026 · aichef.pro/kit-escandallos · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1533,7 @@
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="52" t="inlineStr">
         <is>
-          <t>Carne picada (blend 80/20)</t>
+          <t>Carne picada (mezcla 80/20)</t>
         </is>
       </c>
       <c r="B5" s="53" t="inlineStr">
@@ -1551,19 +1558,19 @@
         </is>
       </c>
       <c r="G5" s="56">
-        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H5" s="57" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="I5" s="20">
         <f>IFERROR(IF(E5="","",E5/(1-H5)),"revisa merma")</f>
-        <v>0.21176470588235294</v>
+        <v>0.18</v>
       </c>
       <c r="J5" s="21">
         <f>IF(G5="?","revisa unidades",IFERROR(I5*D5/G5,""))</f>
-        <v>2.011764705882353</v>
+        <v>1.71</v>
       </c>
       <c r="L5" s="22" t="n"/>
       <c r="M5" s="23" t="n"/>
@@ -1596,7 +1603,7 @@
         </is>
       </c>
       <c r="G6" s="56">
-        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H6" s="57" t="n">
@@ -1641,7 +1648,7 @@
         </is>
       </c>
       <c r="G7" s="56">
-        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H7" s="57" t="n">
@@ -1686,7 +1693,7 @@
         </is>
       </c>
       <c r="G8" s="56">
-        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H8" s="57" t="n">
@@ -1737,7 +1744,7 @@
         </is>
       </c>
       <c r="G9" s="56">
-        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H9" s="57" t="n">
@@ -1782,7 +1789,7 @@
         </is>
       </c>
       <c r="G10" s="56">
-        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H10" s="57" t="n">
@@ -1827,7 +1834,7 @@
         </is>
       </c>
       <c r="G11" s="56">
-        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H11" s="57" t="n">
@@ -1872,7 +1879,7 @@
         </is>
       </c>
       <c r="G12" s="56">
-        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H12" s="57" t="n">
@@ -1897,7 +1904,7 @@
       <c r="E13" s="58" t="n"/>
       <c r="F13" s="58" t="n"/>
       <c r="G13" s="56">
-        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H13" s="59">
@@ -1923,7 +1930,7 @@
       <c r="E14" s="58" t="n"/>
       <c r="F14" s="58" t="n"/>
       <c r="G14" s="56">
-        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H14" s="59">
@@ -1949,7 +1956,7 @@
       <c r="E15" s="58" t="n"/>
       <c r="F15" s="58" t="n"/>
       <c r="G15" s="56">
-        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H15" s="59">
@@ -1974,7 +1981,7 @@
       <c r="E16" s="58" t="n"/>
       <c r="F16" s="58" t="n"/>
       <c r="G16" s="56">
-        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H16" s="59">
@@ -1998,7 +2005,7 @@
       <c r="E17" s="58" t="n"/>
       <c r="F17" s="58" t="n"/>
       <c r="G17" s="56">
-        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H17" s="59">
@@ -2022,7 +2029,7 @@
       <c r="E18" s="58" t="n"/>
       <c r="F18" s="58" t="n"/>
       <c r="G18" s="56">
-        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H18" s="59">
@@ -2046,7 +2053,7 @@
       <c r="E19" s="58" t="n"/>
       <c r="F19" s="58" t="n"/>
       <c r="G19" s="56">
-        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H19" s="59">
@@ -2070,7 +2077,7 @@
       <c r="E20" s="58" t="n"/>
       <c r="F20" s="58" t="n"/>
       <c r="G20" s="56">
-        <f>IF(C20&amp;F20="","",IFERROR(VLOOKUP(C20&amp;"→"&amp;F20,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C20&amp;F20="","",IFERROR(VLOOKUP(C20&amp;"→"&amp;F20,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H20" s="59">
@@ -2094,7 +2101,7 @@
       <c r="E21" s="58" t="n"/>
       <c r="F21" s="58" t="n"/>
       <c r="G21" s="56">
-        <f>IF(C21&amp;F21="","",IFERROR(VLOOKUP(C21&amp;"→"&amp;F21,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C21&amp;F21="","",IFERROR(VLOOKUP(C21&amp;"→"&amp;F21,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H21" s="59">
@@ -2118,7 +2125,7 @@
       <c r="E22" s="58" t="n"/>
       <c r="F22" s="58" t="n"/>
       <c r="G22" s="56">
-        <f>IF(C22&amp;F22="","",IFERROR(VLOOKUP(C22&amp;"→"&amp;F22,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C22&amp;F22="","",IFERROR(VLOOKUP(C22&amp;"→"&amp;F22,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H22" s="59">
@@ -2151,7 +2158,7 @@
       <c r="I24" s="50" t="n"/>
       <c r="J24" s="36">
         <f>SUM(J5:J22)</f>
-        <v>3.1295217608574535</v>
+        <v>2.8277570549751005</v>
       </c>
     </row>
     <row r="25">
@@ -2172,7 +2179,7 @@
       </c>
       <c r="J25" s="38">
         <f>J24*I25</f>
-        <v>0.3129521760857454</v>
+        <v>0.2827757054975101</v>
       </c>
     </row>
     <row r="26">
@@ -2191,7 +2198,7 @@
       <c r="I26" s="50" t="n"/>
       <c r="J26" s="40">
         <f>J24+J25</f>
-        <v>3.4424739369431987</v>
+        <v>3.1105327604726107</v>
       </c>
     </row>
     <row r="27">
@@ -2228,7 +2235,7 @@
       <c r="I28" s="50" t="n"/>
       <c r="J28" s="40">
         <f>IFERROR(J26/I27,"")</f>
-        <v>3.4424739369431987</v>
+        <v>3.1105327604726107</v>
       </c>
     </row>
     <row r="29"/>
@@ -2265,7 +2272,7 @@
       <c r="I31" s="50" t="n"/>
       <c r="J31" s="44">
         <f>IFERROR(J28/I30,"")</f>
-        <v>11.474913123143995</v>
+        <v>10.368442534908702</v>
       </c>
     </row>
     <row r="32">
@@ -2302,7 +2309,7 @@
       <c r="I33" s="50" t="n"/>
       <c r="J33" s="40">
         <f>IFERROR(J31*(1+I32),"")</f>
-        <v>12.622404435458396</v>
+        <v>11.405286788399573</v>
       </c>
     </row>
     <row r="34">
@@ -2321,7 +2328,7 @@
       <c r="I34" s="50" t="n"/>
       <c r="J34" s="44">
         <f>IFERROR(J31-J28,"")</f>
-        <v>8.032439186200797</v>
+        <v>7.257909774436092</v>
       </c>
     </row>
     <row r="35">
@@ -2382,24 +2389,24 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="18">
+    <mergeCell ref="L15:M15"/>
     <mergeCell ref="A30:H30"/>
     <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A34:I34"/>
     <mergeCell ref="L8:M9"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A38:I38"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A33:I33"/>
     <mergeCell ref="A31:I31"/>
-    <mergeCell ref="A33:I33"/>
     <mergeCell ref="A28:I28"/>
     <mergeCell ref="L3:M3"/>
-    <mergeCell ref="A38:I38"/>
-    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A37:H37"/>
     <mergeCell ref="A26:I26"/>
     <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A24:I24"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="A34:I34"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <conditionalFormatting sqref="G5:G22">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
@@ -2561,7 +2568,7 @@
         </is>
       </c>
       <c r="G5" s="56">
-        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H5" s="57" t="n">
@@ -2606,7 +2613,7 @@
         </is>
       </c>
       <c r="G6" s="56">
-        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H6" s="57" t="n">
@@ -2651,7 +2658,7 @@
         </is>
       </c>
       <c r="G7" s="56">
-        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H7" s="57" t="n">
@@ -2676,7 +2683,7 @@
       </c>
       <c r="B8" s="53" t="inlineStr">
         <is>
-          <t>Secos/granos</t>
+          <t>Salsas/condimentos</t>
         </is>
       </c>
       <c r="C8" s="53" t="inlineStr">
@@ -2696,7 +2703,7 @@
         </is>
       </c>
       <c r="G8" s="56">
-        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H8" s="57" t="n">
@@ -2747,7 +2754,7 @@
         </is>
       </c>
       <c r="G9" s="56">
-        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H9" s="57" t="n">
@@ -2792,7 +2799,7 @@
         </is>
       </c>
       <c r="G10" s="56">
-        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H10" s="57" t="n">
@@ -2817,7 +2824,7 @@
       <c r="E11" s="58" t="n"/>
       <c r="F11" s="58" t="n"/>
       <c r="G11" s="56">
-        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H11" s="59">
@@ -2843,7 +2850,7 @@
       <c r="E12" s="58" t="n"/>
       <c r="F12" s="58" t="n"/>
       <c r="G12" s="56">
-        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H12" s="59">
@@ -2869,7 +2876,7 @@
       <c r="E13" s="58" t="n"/>
       <c r="F13" s="58" t="n"/>
       <c r="G13" s="56">
-        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H13" s="59">
@@ -2895,7 +2902,7 @@
       <c r="E14" s="58" t="n"/>
       <c r="F14" s="58" t="n"/>
       <c r="G14" s="56">
-        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H14" s="59">
@@ -2921,7 +2928,7 @@
       <c r="E15" s="58" t="n"/>
       <c r="F15" s="58" t="n"/>
       <c r="G15" s="56">
-        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H15" s="59">
@@ -2946,7 +2953,7 @@
       <c r="E16" s="58" t="n"/>
       <c r="F16" s="58" t="n"/>
       <c r="G16" s="56">
-        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H16" s="59">
@@ -2971,7 +2978,7 @@
       <c r="E17" s="58" t="n"/>
       <c r="F17" s="58" t="n"/>
       <c r="G17" s="56">
-        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H17" s="59">
@@ -2996,7 +3003,7 @@
       <c r="E18" s="58" t="n"/>
       <c r="F18" s="58" t="n"/>
       <c r="G18" s="56">
-        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H18" s="59">
@@ -3021,7 +3028,7 @@
       <c r="E19" s="58" t="n"/>
       <c r="F19" s="58" t="n"/>
       <c r="G19" s="56">
-        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H19" s="59">
@@ -3046,7 +3053,7 @@
       <c r="E20" s="58" t="n"/>
       <c r="F20" s="58" t="n"/>
       <c r="G20" s="56">
-        <f>IF(C20&amp;F20="","",IFERROR(VLOOKUP(C20&amp;"→"&amp;F20,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C20&amp;F20="","",IFERROR(VLOOKUP(C20&amp;"→"&amp;F20,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H20" s="59">
@@ -3312,23 +3319,23 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="18">
     <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A32:I32"/>
     <mergeCell ref="L8:M9"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A35:H35"/>
     <mergeCell ref="A31:I31"/>
     <mergeCell ref="A33:I33"/>
     <mergeCell ref="A36:I36"/>
     <mergeCell ref="L3:M3"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A25:H25"/>
     <mergeCell ref="A29:I29"/>
-    <mergeCell ref="A26:I26"/>
-    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A24:I24"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="A35:H35"/>
-    <mergeCell ref="A22:I22"/>
-    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <conditionalFormatting sqref="G5:G20">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
@@ -3490,7 +3497,7 @@
         </is>
       </c>
       <c r="G5" s="56">
-        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H5" s="57" t="n">
@@ -3535,7 +3542,7 @@
         </is>
       </c>
       <c r="G6" s="56">
-        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H6" s="57" t="n">
@@ -3580,7 +3587,7 @@
         </is>
       </c>
       <c r="G7" s="56">
-        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H7" s="57" t="n">
@@ -3605,7 +3612,7 @@
       </c>
       <c r="B8" s="53" t="inlineStr">
         <is>
-          <t>Secos/granos</t>
+          <t>Salsas/condimentos</t>
         </is>
       </c>
       <c r="C8" s="53" t="inlineStr">
@@ -3625,7 +3632,7 @@
         </is>
       </c>
       <c r="G8" s="56">
-        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H8" s="57" t="n">
@@ -3676,7 +3683,7 @@
         </is>
       </c>
       <c r="G9" s="56">
-        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H9" s="57" t="n">
@@ -3701,7 +3708,7 @@
       <c r="E10" s="58" t="n"/>
       <c r="F10" s="58" t="n"/>
       <c r="G10" s="56">
-        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H10" s="59">
@@ -3727,7 +3734,7 @@
       <c r="E11" s="58" t="n"/>
       <c r="F11" s="58" t="n"/>
       <c r="G11" s="56">
-        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H11" s="59">
@@ -3753,7 +3760,7 @@
       <c r="E12" s="58" t="n"/>
       <c r="F12" s="58" t="n"/>
       <c r="G12" s="56">
-        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H12" s="59">
@@ -3779,7 +3786,7 @@
       <c r="E13" s="58" t="n"/>
       <c r="F13" s="58" t="n"/>
       <c r="G13" s="56">
-        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H13" s="59">
@@ -3805,7 +3812,7 @@
       <c r="E14" s="58" t="n"/>
       <c r="F14" s="58" t="n"/>
       <c r="G14" s="56">
-        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H14" s="59">
@@ -3831,7 +3838,7 @@
       <c r="E15" s="58" t="n"/>
       <c r="F15" s="58" t="n"/>
       <c r="G15" s="56">
-        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H15" s="59">
@@ -3857,7 +3864,7 @@
       <c r="E16" s="58" t="n"/>
       <c r="F16" s="58" t="n"/>
       <c r="G16" s="56">
-        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H16" s="59">
@@ -3883,7 +3890,7 @@
       <c r="E17" s="58" t="n"/>
       <c r="F17" s="58" t="n"/>
       <c r="G17" s="56">
-        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H17" s="59">
@@ -3909,7 +3916,7 @@
       <c r="E18" s="58" t="n"/>
       <c r="F18" s="58" t="n"/>
       <c r="G18" s="56">
-        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H18" s="59">
@@ -3935,7 +3942,7 @@
       <c r="E19" s="58" t="n"/>
       <c r="F19" s="58" t="n"/>
       <c r="G19" s="56">
-        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H19" s="59">
@@ -4204,20 +4211,20 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="18">
     <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A23:I23"/>
     <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A35:I35"/>
     <mergeCell ref="L8:M9"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A22:H22"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="A27:H27"/>
     <mergeCell ref="A31:I31"/>
+    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A28:I28"/>
     <mergeCell ref="L3:M3"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="A30:I30"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A24:H24"/>
     <mergeCell ref="A21:I21"/>
     <mergeCell ref="A1:J1"/>
@@ -4417,15 +4424,15 @@
       </c>
       <c r="B16" s="72">
         <f>IF('Smash Burger'!$I$37="",'Smash Burger'!$J$31,'Smash Burger'!$I$37)</f>
-        <v>11.474913123143995</v>
+        <v>10.368442534908702</v>
       </c>
       <c r="C16" s="72">
         <f>'Smash Burger'!$J$28</f>
-        <v>3.4424739369431987</v>
+        <v>3.1105327604726107</v>
       </c>
       <c r="D16" s="73">
         <f>IFERROR(B16-C16,"")</f>
-        <v>8.032439186200797</v>
+        <v>7.257909774436092</v>
       </c>
       <c r="E16" s="74" t="n">
         <v>0.5</v>
@@ -4483,7 +4490,7 @@
       </c>
       <c r="B19" s="73">
         <f>IFERROR(SUMPRODUCT(B16:B18,E16:E18)/SUM(E16:E18),"")</f>
-        <v>11.344968378580255</v>
+        <v>10.79173308446261</v>
       </c>
     </row>
     <row r="20">
@@ -4494,7 +4501,7 @@
       </c>
       <c r="B20" s="71">
         <f>IFERROR(SUMPRODUCT(D16:D18,E16:E18)/SUM(E16:E18),"")</f>
-        <v>7.94147786500618</v>
+        <v>7.554213159123827</v>
       </c>
     </row>
     <row r="21"/>
@@ -4513,7 +4520,7 @@
       </c>
       <c r="B23" s="75">
         <f>IFERROR(ROUNDUP(B12/B20,0),"")</f>
-        <v>38.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="24">
@@ -4524,7 +4531,7 @@
       </c>
       <c r="B24" s="72">
         <f>IFERROR(B23*B19,"")</f>
-        <v>431.10879838604967</v>
+        <v>431.6693233785044</v>
       </c>
     </row>
     <row r="25">
@@ -4545,7 +4552,7 @@
       </c>
       <c r="B26" s="72">
         <f>IFERROR(B24*(1+B25),"")</f>
-        <v>474.2196782246547</v>
+        <v>474.83625571635486</v>
       </c>
     </row>
     <row r="27"/>
@@ -4585,7 +4592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4603,7 +4610,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>La usa la columna «Factor» de cada escandallo. Puedes añadir parejas al final: la clave se escribe «compra→uso».</t>
+          <t>La usa la columna «Factor» de cada escandallo. Puedes añadir parejas al final, hasta la fila 67: la clave se escribe «compra→uso».</t>
         </is>
       </c>
     </row>
@@ -5120,6 +5127,7 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
   </sheetData>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -5163,7 +5171,13 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Mide tu merma real con la plantilla 12 (Test de Rendimiento) y llévala a «Merma (%)» de la ficha.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="77" t="inlineStr">
         <is>
